--- a/artfynd/A 58567-2025 artfynd.xlsx
+++ b/artfynd/A 58567-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130010008</v>
       </c>
       <c r="B2" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>130004898</v>
       </c>
       <c r="B4" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58567-2025 artfynd.xlsx
+++ b/artfynd/A 58567-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130010008</v>
       </c>
       <c r="B2" t="n">
-        <v>97669</v>
+        <v>97686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>130004898</v>
       </c>
       <c r="B4" t="n">
-        <v>97669</v>
+        <v>97686</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58567-2025 artfynd.xlsx
+++ b/artfynd/A 58567-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>130010008</v>
       </c>
       <c r="B2" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>130004898</v>
       </c>
       <c r="B4" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130004838</v>
+        <v>130004683</v>
       </c>
       <c r="B6" t="n">
         <v>57738</v>
@@ -1156,13 +1156,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>336097</v>
+        <v>336146</v>
       </c>
       <c r="R6" t="n">
-        <v>6439094</v>
+        <v>6439144</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1201,12 +1201,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,19 +1216,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130004683</v>
+        <v>130004838</v>
       </c>
       <c r="B7" t="n">
         <v>57738</v>
@@ -1268,13 +1263,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>336146</v>
+        <v>336097</v>
       </c>
       <c r="R7" t="n">
-        <v>6439144</v>
+        <v>6439094</v>
       </c>
       <c r="S7" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,7 +1298,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1313,7 +1308,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1328,12 +1328,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1458,6 +1458,949 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130242210</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57738</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Spillkråka 3, Spillkråka 2, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>336205</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6438893</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130251677</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57738</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nygård, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>336379</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6439284</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130252237</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57738</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nygård, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>336284</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6438978</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ann-Charlotte Svensson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ann-Charlotte Svensson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130251702</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57738</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nygård, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>336266</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6439258</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130251551</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57738</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Nygård, Vg</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>336220</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6439020</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130241652</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97706</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skövde, Skövde, Vg</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>336142</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6438887</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130251711</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57738</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nygård, Vg</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>336183</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6439167</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130251638</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57738</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nygård, Vg</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>336328</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6439197</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130241931</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57738</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Spillkråka, Björk, Vg</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>336142</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6438887</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Relativt färska, typ medelfärska spår på död tall</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58567-2025 artfynd.xlsx
+++ b/artfynd/A 58567-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>130010008</v>
       </c>
       <c r="B2" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>130003673</v>
       </c>
       <c r="B3" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>130004898</v>
       </c>
       <c r="B4" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>130006704</v>
       </c>
       <c r="B5" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130004683</v>
+        <v>130004838</v>
       </c>
       <c r="B6" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,13 +1156,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>336146</v>
+        <v>336097</v>
       </c>
       <c r="R6" t="n">
-        <v>6439144</v>
+        <v>6439094</v>
       </c>
       <c r="S6" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1201,7 +1201,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1216,22 +1221,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130004838</v>
+        <v>130004683</v>
       </c>
       <c r="B7" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1263,13 +1268,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>336097</v>
+        <v>336146</v>
       </c>
       <c r="R7" t="n">
-        <v>6439094</v>
+        <v>6439144</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1298,7 +1303,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1308,12 +1313,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1328,12 +1328,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1343,7 +1343,7 @@
         <v>130010034</v>
       </c>
       <c r="B8" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>130242210</v>
       </c>
       <c r="B9" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1567,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130251677</v>
+        <v>130251590</v>
       </c>
       <c r="B10" t="n">
-        <v>57738</v>
+        <v>56399</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,21 +1578,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>206004</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>336379</v>
+        <v>336315</v>
       </c>
       <c r="R10" t="n">
-        <v>6439284</v>
+        <v>6439275</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130252237</v>
+        <v>130251677</v>
       </c>
       <c r="B11" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,13 +1707,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>336284</v>
+        <v>336379</v>
       </c>
       <c r="R11" t="n">
-        <v>6438978</v>
+        <v>6439284</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1740,19 +1740,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,22 +1757,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130251702</v>
+        <v>130252237</v>
       </c>
       <c r="B12" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1818,13 +1808,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>336266</v>
+        <v>336284</v>
       </c>
       <c r="R12" t="n">
-        <v>6439258</v>
+        <v>6438978</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1851,9 +1841,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1868,22 +1868,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Ann-Charlotte Svensson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Ann-Charlotte Svensson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130251551</v>
+        <v>130251702</v>
       </c>
       <c r="B13" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>336220</v>
+        <v>336266</v>
       </c>
       <c r="R13" t="n">
-        <v>6439020</v>
+        <v>6439258</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1981,44 +1981,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130241652</v>
+        <v>130251551</v>
       </c>
       <c r="B14" t="n">
-        <v>97706</v>
+        <v>57823</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>224363</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skövde, Skövde, Vg</t>
+          <t>Nygård, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>336142</v>
+        <v>336220</v>
       </c>
       <c r="R14" t="n">
-        <v>6438887</v>
+        <v>6439020</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2045,19 +2053,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2072,64 +2070,56 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130251711</v>
+        <v>130241652</v>
       </c>
       <c r="B15" t="n">
-        <v>57738</v>
+        <v>97793</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>224363</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nygård, Vg</t>
+          <t>Skövde, Skövde, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>336183</v>
+        <v>336142</v>
       </c>
       <c r="R15" t="n">
-        <v>6439167</v>
+        <v>6438887</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2156,9 +2146,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,22 +2173,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130251638</v>
+        <v>130251711</v>
       </c>
       <c r="B16" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>336328</v>
+        <v>336183</v>
       </c>
       <c r="R16" t="n">
-        <v>6439197</v>
+        <v>6439167</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2286,10 +2286,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130241931</v>
+        <v>130251638</v>
       </c>
       <c r="B17" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,24 +2315,23 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Spillkråka, Björk, Vg</t>
+          <t>Nygård, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>336142</v>
+        <v>336328</v>
       </c>
       <c r="R17" t="n">
-        <v>6438887</v>
+        <v>6439197</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2359,24 +2358,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Relativt färska, typ medelfärska spår på död tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2391,15 +2375,132 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130241931</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Spillkråka, Björk, Vg</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>336142</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6438887</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Relativt färska, typ medelfärska spår på död tall</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
           <t>Linus Lundin</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
+      <c r="AX18" t="inlineStr">
         <is>
           <t>Linus Lundin</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58567-2025 artfynd.xlsx
+++ b/artfynd/A 58567-2025 artfynd.xlsx
@@ -2286,7 +2286,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130251638</v>
+        <v>130241931</v>
       </c>
       <c r="B17" t="n">
         <v>57823</v>
@@ -2315,23 +2315,24 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nygård, Vg</t>
+          <t>Spillkråka, Björk, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>336328</v>
+        <v>336142</v>
       </c>
       <c r="R17" t="n">
-        <v>6439197</v>
+        <v>6438887</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2358,9 +2359,24 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Relativt färska, typ medelfärska spår på död tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2375,19 +2391,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130241931</v>
+        <v>130251638</v>
       </c>
       <c r="B18" t="n">
         <v>57823</v>
@@ -2416,24 +2432,23 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Spillkråka, Björk, Vg</t>
+          <t>Nygård, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>336142</v>
+        <v>336328</v>
       </c>
       <c r="R18" t="n">
-        <v>6438887</v>
+        <v>6439197</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2460,24 +2475,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Relativt färska, typ medelfärska spår på död tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2492,12 +2492,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 58567-2025 artfynd.xlsx
+++ b/artfynd/A 58567-2025 artfynd.xlsx
@@ -2286,7 +2286,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130241931</v>
+        <v>130251638</v>
       </c>
       <c r="B17" t="n">
         <v>57823</v>
@@ -2315,24 +2315,23 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Spillkråka, Björk, Vg</t>
+          <t>Nygård, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>336142</v>
+        <v>336328</v>
       </c>
       <c r="R17" t="n">
-        <v>6438887</v>
+        <v>6439197</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2359,24 +2358,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Relativt färska, typ medelfärska spår på död tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2391,19 +2375,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130251638</v>
+        <v>130241931</v>
       </c>
       <c r="B18" t="n">
         <v>57823</v>
@@ -2432,23 +2416,24 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nygård, Vg</t>
+          <t>Spillkråka, Björk, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>336328</v>
+        <v>336142</v>
       </c>
       <c r="R18" t="n">
-        <v>6439197</v>
+        <v>6438887</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2475,9 +2460,24 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Relativt färska, typ medelfärska spår på död tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2492,12 +2492,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 58567-2025 artfynd.xlsx
+++ b/artfynd/A 58567-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2085,7 +2085,7 @@
         <v>130241652</v>
       </c>
       <c r="B15" t="n">
-        <v>97793</v>
+        <v>97796</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130241931</v>
+        <v>130251638</v>
       </c>
       <c r="B17" t="n">
         <v>57823</v>
@@ -2315,24 +2315,23 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Spillkråka, Björk, Vg</t>
+          <t>Nygård, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>336142</v>
+        <v>336328</v>
       </c>
       <c r="R17" t="n">
-        <v>6438887</v>
+        <v>6439197</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2359,24 +2358,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Relativt färska, typ medelfärska spår på död tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2391,19 +2375,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130251638</v>
+        <v>130241931</v>
       </c>
       <c r="B18" t="n">
         <v>57823</v>
@@ -2432,23 +2416,24 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nygård, Vg</t>
+          <t>Spillkråka, Björk, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>336328</v>
+        <v>336142</v>
       </c>
       <c r="R18" t="n">
-        <v>6439197</v>
+        <v>6438887</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2475,9 +2460,24 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Relativt färska, typ medelfärska spår på död tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2492,15 +2492,121 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130616003</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58224</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Nygård 1, Vg</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>336191</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6438976</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Inspelat material med Audiomoth ljudbox</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58567-2025 artfynd.xlsx
+++ b/artfynd/A 58567-2025 artfynd.xlsx
@@ -1463,7 +1463,7 @@
         <v>130242210</v>
       </c>
       <c r="B9" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>130251590</v>
       </c>
       <c r="B10" t="n">
-        <v>56399</v>
+        <v>56425</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>130251677</v>
       </c>
       <c r="B11" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>130252237</v>
       </c>
       <c r="B12" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>130251702</v>
       </c>
       <c r="B13" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>130251551</v>
       </c>
       <c r="B14" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>130241652</v>
       </c>
       <c r="B15" t="n">
-        <v>97796</v>
+        <v>97822</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>130251711</v>
       </c>
       <c r="B16" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2286,10 +2286,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130251638</v>
+        <v>130241931</v>
       </c>
       <c r="B17" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,23 +2315,24 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nygård, Vg</t>
+          <t>Spillkråka, Björk, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>336328</v>
+        <v>336142</v>
       </c>
       <c r="R17" t="n">
-        <v>6439197</v>
+        <v>6438887</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2358,9 +2359,24 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Relativt färska, typ medelfärska spår på död tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2375,22 +2391,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130241931</v>
+        <v>130251638</v>
       </c>
       <c r="B18" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2416,24 +2432,23 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Spillkråka, Björk, Vg</t>
+          <t>Nygård, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>336142</v>
+        <v>336328</v>
       </c>
       <c r="R18" t="n">
-        <v>6438887</v>
+        <v>6439197</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2460,24 +2475,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Relativt färska, typ medelfärska spår på död tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2492,12 +2492,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 58567-2025 artfynd.xlsx
+++ b/artfynd/A 58567-2025 artfynd.xlsx
@@ -2085,7 +2085,7 @@
         <v>130241652</v>
       </c>
       <c r="B15" t="n">
-        <v>97822</v>
+        <v>97823</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 58567-2025 artfynd.xlsx
+++ b/artfynd/A 58567-2025 artfynd.xlsx
@@ -2085,7 +2085,7 @@
         <v>130241652</v>
       </c>
       <c r="B15" t="n">
-        <v>97823</v>
+        <v>97824</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130241931</v>
+        <v>130251638</v>
       </c>
       <c r="B17" t="n">
         <v>57849</v>
@@ -2315,24 +2315,23 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Spillkråka, Björk, Vg</t>
+          <t>Nygård, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>336142</v>
+        <v>336328</v>
       </c>
       <c r="R17" t="n">
-        <v>6438887</v>
+        <v>6439197</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2359,24 +2358,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Relativt färska, typ medelfärska spår på död tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2391,19 +2375,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130251638</v>
+        <v>130241931</v>
       </c>
       <c r="B18" t="n">
         <v>57849</v>
@@ -2432,23 +2416,24 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nygård, Vg</t>
+          <t>Spillkråka, Björk, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>336328</v>
+        <v>336142</v>
       </c>
       <c r="R18" t="n">
-        <v>6439197</v>
+        <v>6438887</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2475,9 +2460,24 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Relativt färska, typ medelfärska spår på död tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2492,12 +2492,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 58567-2025 artfynd.xlsx
+++ b/artfynd/A 58567-2025 artfynd.xlsx
@@ -1463,7 +1463,7 @@
         <v>130242210</v>
       </c>
       <c r="B9" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>130251590</v>
       </c>
       <c r="B10" t="n">
-        <v>56425</v>
+        <v>56427</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>130251677</v>
       </c>
       <c r="B11" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>130252237</v>
       </c>
       <c r="B12" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>130251702</v>
       </c>
       <c r="B13" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>130251551</v>
       </c>
       <c r="B14" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>130241652</v>
       </c>
       <c r="B15" t="n">
-        <v>97824</v>
+        <v>97826</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>130251711</v>
       </c>
       <c r="B16" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2286,10 +2286,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130251638</v>
+        <v>130241931</v>
       </c>
       <c r="B17" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,23 +2315,24 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nygård, Vg</t>
+          <t>Spillkråka, Björk, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>336328</v>
+        <v>336142</v>
       </c>
       <c r="R17" t="n">
-        <v>6439197</v>
+        <v>6438887</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2358,9 +2359,24 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Relativt färska, typ medelfärska spår på död tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2375,22 +2391,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130241931</v>
+        <v>130251638</v>
       </c>
       <c r="B18" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2416,24 +2432,23 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Spillkråka, Björk, Vg</t>
+          <t>Nygård, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>336142</v>
+        <v>336328</v>
       </c>
       <c r="R18" t="n">
-        <v>6438887</v>
+        <v>6439197</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2460,24 +2475,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Relativt färska, typ medelfärska spår på död tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2492,12 +2492,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2507,7 +2507,7 @@
         <v>130616003</v>
       </c>
       <c r="B19" t="n">
-        <v>58224</v>
+        <v>58226</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 58567-2025 artfynd.xlsx
+++ b/artfynd/A 58567-2025 artfynd.xlsx
@@ -2085,7 +2085,7 @@
         <v>130241652</v>
       </c>
       <c r="B15" t="n">
-        <v>97826</v>
+        <v>97830</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 58567-2025 artfynd.xlsx
+++ b/artfynd/A 58567-2025 artfynd.xlsx
@@ -2286,7 +2286,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130241931</v>
+        <v>130251638</v>
       </c>
       <c r="B17" t="n">
         <v>57851</v>
@@ -2315,24 +2315,23 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Spillkråka, Björk, Vg</t>
+          <t>Nygård, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>336142</v>
+        <v>336328</v>
       </c>
       <c r="R17" t="n">
-        <v>6438887</v>
+        <v>6439197</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2359,24 +2358,9 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Relativt färska, typ medelfärska spår på död tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2391,19 +2375,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130251638</v>
+        <v>130241931</v>
       </c>
       <c r="B18" t="n">
         <v>57851</v>
@@ -2432,23 +2416,24 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nygård, Vg</t>
+          <t>Spillkråka, Björk, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>336328</v>
+        <v>336142</v>
       </c>
       <c r="R18" t="n">
-        <v>6439197</v>
+        <v>6438887</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2475,9 +2460,24 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Relativt färska, typ medelfärska spår på död tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2492,12 +2492,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 58567-2025 artfynd.xlsx
+++ b/artfynd/A 58567-2025 artfynd.xlsx
@@ -2507,7 +2507,7 @@
         <v>130616003</v>
       </c>
       <c r="B19" t="n">
-        <v>58226</v>
+        <v>58234</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 58567-2025 artfynd.xlsx
+++ b/artfynd/A 58567-2025 artfynd.xlsx
@@ -2507,7 +2507,7 @@
         <v>130616003</v>
       </c>
       <c r="B19" t="n">
-        <v>58234</v>
+        <v>58235</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 58567-2025 artfynd.xlsx
+++ b/artfynd/A 58567-2025 artfynd.xlsx
@@ -2507,7 +2507,7 @@
         <v>130616003</v>
       </c>
       <c r="B19" t="n">
-        <v>58235</v>
+        <v>58236</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 58567-2025 artfynd.xlsx
+++ b/artfynd/A 58567-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2608,6 +2608,120 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130868238</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57861</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Nygård 3, Vg</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>336329</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6439113</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Inspelad med Audiomoth ljudbox på platsen.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58567-2025 artfynd.xlsx
+++ b/artfynd/A 58567-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,6 +2722,112 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130348534</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57861</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Nygård, Vg</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>336180</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6438978</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ale-Skövde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Födosök i träd</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58567-2025 artfynd.xlsx
+++ b/artfynd/A 58567-2025 artfynd.xlsx
@@ -2507,7 +2507,7 @@
         <v>130616003</v>
       </c>
       <c r="B19" t="n">
-        <v>58236</v>
+        <v>58250</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>130868238</v>
       </c>
       <c r="B20" t="n">
-        <v>57861</v>
+        <v>57875</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>130348534</v>
       </c>
       <c r="B21" t="n">
-        <v>57861</v>
+        <v>57875</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 58567-2025 artfynd.xlsx
+++ b/artfynd/A 58567-2025 artfynd.xlsx
@@ -2833,7 +2833,7 @@
         <v>131036113</v>
       </c>
       <c r="B22" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 58567-2025 artfynd.xlsx
+++ b/artfynd/A 58567-2025 artfynd.xlsx
@@ -2833,7 +2833,7 @@
         <v>131036113</v>
       </c>
       <c r="B22" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
